--- a/wykres_skalowania_joy.xlsx
+++ b/wykres_skalowania_joy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Luke\FlexRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8D5F88-0F90-47EB-A84A-BAE3255CA7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED28FA02-53F7-4454-B6F0-CF2CA3E7E24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1763" yWindow="-98" windowWidth="22335" windowHeight="13695" activeTab="3" xr2:uid="{81982E8A-BA81-4862-A7E8-94F1A526E7CC}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="162">
   <si>
     <t>Kolumna1</t>
   </si>
@@ -426,21 +426,9 @@
     <t>5x KEY</t>
   </si>
   <si>
-    <t>SW 2</t>
-  </si>
-  <si>
-    <t>SW 3</t>
-  </si>
-  <si>
-    <t>3x LED RGB</t>
-  </si>
-  <si>
     <t>OLED</t>
   </si>
   <si>
-    <t>BUZZER</t>
-  </si>
-  <si>
     <t>IMU</t>
   </si>
   <si>
@@ -462,9 +450,6 @@
     <t>I2C</t>
   </si>
   <si>
-    <t>PWM</t>
-  </si>
-  <si>
     <t>SPI</t>
   </si>
   <si>
@@ -652,6 +637,33 @@
   </si>
   <si>
     <t>??</t>
+  </si>
+  <si>
+    <t>Potencjometr montażowy leżący 10kΩ - 5szt.</t>
+  </si>
+  <si>
+    <t>Przełącznik monostabilny PB07C 7x7mm - 5 szt.</t>
+  </si>
+  <si>
+    <t>Mikroprzełącznik bistabilny ON-ON 7x7mm 5szt.</t>
+  </si>
+  <si>
+    <t>Tact Switch 12x12, 7mm THT 6pin - białe podświetlenie - 5szt.</t>
+  </si>
+  <si>
+    <t>Przełącznik suwakowy ESP2010 - kątowy</t>
+  </si>
+  <si>
+    <t>bezpieczniki polimerowe</t>
+  </si>
+  <si>
+    <t>2-3 FUN. KEYS</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>3-5x LED RGB</t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1044,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1051,13 +1063,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1068,7 +1073,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1103,26 +1108,11 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1131,7 +1121,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1167,7 +1157,25 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
@@ -6874,7 +6882,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2702BDD6-77D0-46D1-94A1-7EBAD4BA6947}">
-  <dimension ref="C1:AC43"/>
+  <dimension ref="C1:AC48"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="14.73046875" customWidth="1"/>
@@ -6888,525 +6896,509 @@
   <sheetData>
     <row r="1" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="2" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C2" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="I2" s="11" t="s">
+      <c r="D2" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" s="53" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="12"/>
+      <c r="J2" s="54"/>
     </row>
     <row r="3" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="14">
         <v>2</v>
       </c>
-      <c r="E3" s="17">
+      <c r="E3" s="14">
         <v>1</v>
       </c>
-      <c r="F3" s="18"/>
+      <c r="F3" s="15"/>
       <c r="H3" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" t="s">
         <v>68</v>
       </c>
-      <c r="AC3" s="31" t="s">
-        <v>103</v>
+      <c r="AC3" s="28" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="14">
         <v>2</v>
       </c>
-      <c r="E4" s="17">
+      <c r="E4" s="14">
         <v>1</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="I4" s="25" t="s">
+      <c r="F4" s="15"/>
+      <c r="I4" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" s="11" t="s">
         <v>47</v>
       </c>
       <c r="K4" t="s">
         <v>69</v>
       </c>
-      <c r="U4" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="36"/>
+      <c r="U4" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="V4" s="56"/>
+      <c r="W4" s="56"/>
+      <c r="X4" s="57"/>
     </row>
     <row r="5" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D5" s="17">
+      <c r="D5" s="14">
         <v>1</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
-      <c r="I5" s="29" t="s">
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
+      <c r="I5" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="11" t="s">
         <v>48</v>
       </c>
       <c r="K5" t="s">
         <v>70</v>
       </c>
       <c r="T5" s="9"/>
-      <c r="U5" s="46">
+      <c r="U5" s="38">
         <v>40</v>
       </c>
-      <c r="V5" s="54" t="s">
-        <v>105</v>
-      </c>
-      <c r="W5" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="X5" s="49">
+      <c r="V5" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="W5" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="X5" s="41">
         <v>1</v>
       </c>
-      <c r="Y5" s="33" t="s">
-        <v>137</v>
+      <c r="Y5" s="29" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C6" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17">
-        <v>1</v>
-      </c>
-      <c r="F6" s="18"/>
+      <c r="C6" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="F6" s="15"/>
       <c r="H6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="I6" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="J6" s="14" t="s">
+      <c r="I6" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="K6" s="10" t="s">
+      <c r="K6" t="s">
         <v>71</v>
       </c>
-      <c r="T6" s="52" t="s">
-        <v>142</v>
-      </c>
-      <c r="U6" s="47">
+      <c r="T6" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="U6" s="39">
         <v>39</v>
       </c>
-      <c r="V6" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="W6" s="43" t="s">
-        <v>136</v>
-      </c>
-      <c r="X6" s="50">
+      <c r="V6" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="W6" s="35" t="s">
+        <v>131</v>
+      </c>
+      <c r="X6" s="42">
         <v>2</v>
       </c>
-      <c r="Y6" s="33" t="s">
-        <v>138</v>
+      <c r="Y6" s="29" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C7" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17">
-        <v>2</v>
-      </c>
-      <c r="F7" s="18"/>
+      <c r="C7" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14">
+        <v>1</v>
+      </c>
+      <c r="F7" s="15"/>
       <c r="H7" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="J7" s="14" t="s">
+      <c r="I7" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="K7" s="10" t="s">
+      <c r="K7" t="s">
         <v>72</v>
       </c>
-      <c r="T7" s="53" t="s">
+      <c r="T7" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="U7" s="47">
+      <c r="U7" s="39">
         <v>38</v>
       </c>
-      <c r="V7" s="39" t="s">
+      <c r="V7" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="W7" s="44" t="s">
+      <c r="W7" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="X7" s="50">
+      <c r="X7" s="42">
         <v>3</v>
       </c>
-      <c r="Y7" s="33"/>
+      <c r="Y7" s="29"/>
     </row>
     <row r="8" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C8" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17">
-        <v>1</v>
-      </c>
-      <c r="F8" s="18"/>
+      <c r="C8" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15" t="s">
+        <v>89</v>
+      </c>
       <c r="H8" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="I8" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="J8" s="14" t="s">
+      <c r="I8" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" t="s">
         <v>73</v>
       </c>
       <c r="T8" s="9"/>
-      <c r="U8" s="47">
+      <c r="U8" s="39">
         <v>37</v>
       </c>
-      <c r="V8" s="55" t="s">
-        <v>107</v>
-      </c>
-      <c r="W8" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="X8" s="50">
+      <c r="V8" s="47" t="s">
+        <v>102</v>
+      </c>
+      <c r="W8" s="35" t="s">
+        <v>126</v>
+      </c>
+      <c r="X8" s="42">
         <v>4</v>
       </c>
-      <c r="Y8" s="33" t="s">
-        <v>139</v>
+      <c r="Y8" s="29" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C9" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="17"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="18" t="s">
-        <v>93</v>
+      <c r="C9" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15" t="s">
+        <v>89</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="J9" s="14" t="s">
+      <c r="I9" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" t="s">
         <v>74</v>
       </c>
       <c r="T9" s="9"/>
-      <c r="U9" s="47">
+      <c r="U9" s="39">
         <v>36</v>
       </c>
-      <c r="V9" s="55" t="s">
-        <v>108</v>
-      </c>
-      <c r="W9" s="43" t="s">
-        <v>132</v>
-      </c>
-      <c r="X9" s="50">
+      <c r="V9" s="47" t="s">
+        <v>103</v>
+      </c>
+      <c r="W9" s="35" t="s">
+        <v>127</v>
+      </c>
+      <c r="X9" s="42">
         <v>5</v>
       </c>
-      <c r="Y9" s="33" t="s">
-        <v>140</v>
+      <c r="Y9" s="29" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C10" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="18"/>
+      <c r="C10" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15" t="s">
+        <v>90</v>
+      </c>
       <c r="H10" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="I10" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="J10" s="14" t="s">
+      <c r="I10" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="K10" t="s">
         <v>75</v>
       </c>
-      <c r="U10" s="47">
+      <c r="U10" s="39">
         <v>35</v>
       </c>
-      <c r="V10" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="W10" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="X10" s="50">
+      <c r="V10" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="W10" s="35" t="s">
+        <v>128</v>
+      </c>
+      <c r="X10" s="42">
         <v>6</v>
       </c>
-      <c r="Y10" s="33" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="3:29" x14ac:dyDescent="0.45">
+      <c r="Y10" s="29" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C11" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="17"/>
+        <v>85</v>
+      </c>
+      <c r="D11" s="17">
+        <v>1</v>
+      </c>
       <c r="E11" s="17"/>
-      <c r="F11" s="18" t="s">
-        <v>93</v>
-      </c>
+      <c r="F11" s="18"/>
       <c r="H11" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="J11" s="14" t="s">
+      <c r="I11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="10" t="s">
+      <c r="K11" t="s">
         <v>76</v>
       </c>
-      <c r="U11" s="47">
+      <c r="U11" s="39">
         <v>34</v>
       </c>
-      <c r="V11" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="W11" s="43" t="s">
-        <v>134</v>
-      </c>
-      <c r="X11" s="50">
+      <c r="V11" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="W11" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="X11" s="42">
         <v>7</v>
       </c>
-      <c r="Y11" s="34" t="s">
+      <c r="Y11" s="29" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="12" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="C12" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="18" t="s">
-        <v>95</v>
-      </c>
       <c r="H12" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="I12" s="13" t="s">
+      <c r="I12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="K12" t="s">
         <v>77</v>
       </c>
-      <c r="U12" s="47">
+      <c r="U12" s="39">
         <v>33</v>
       </c>
-      <c r="V12" s="39" t="s">
+      <c r="V12" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="W12" s="44" t="s">
+      <c r="W12" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="X12" s="50">
+      <c r="X12" s="42">
         <v>8</v>
       </c>
-      <c r="Y12" s="33"/>
-    </row>
-    <row r="13" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C13" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="20">
-        <v>1</v>
-      </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="21"/>
+      <c r="Y12" s="29"/>
+    </row>
+    <row r="13" spans="3:29" x14ac:dyDescent="0.45">
       <c r="H13" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I13" s="13" t="s">
+      <c r="I13" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" t="s">
         <v>78</v>
       </c>
-      <c r="T13" s="32" t="s">
+      <c r="T13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="U13" s="47">
+      <c r="U13" s="39">
         <v>32</v>
       </c>
-      <c r="V13" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="W13" s="43" t="s">
-        <v>127</v>
-      </c>
-      <c r="X13" s="50">
+      <c r="V13" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="W13" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="X13" s="42">
         <v>9</v>
       </c>
-      <c r="Y13" s="33" t="s">
+      <c r="Y13" s="29" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="14" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="T14" s="32" t="s">
+      <c r="T14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="U14" s="47">
+      <c r="U14" s="39">
         <v>31</v>
       </c>
-      <c r="V14" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="W14" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="X14" s="50">
+      <c r="V14" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="W14" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="X14" s="42">
         <v>10</v>
       </c>
-      <c r="Y14" s="33" t="s">
+      <c r="Y14" s="29" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="J15" s="30" t="s">
+      <c r="J15" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="U15" s="47">
+      <c r="U15" s="39">
         <v>30</v>
       </c>
-      <c r="V15" s="55" t="s">
-        <v>113</v>
-      </c>
-      <c r="W15" s="43" t="s">
-        <v>129</v>
-      </c>
-      <c r="X15" s="50">
+      <c r="V15" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="W15" s="35" t="s">
+        <v>124</v>
+      </c>
+      <c r="X15" s="42">
         <v>11</v>
       </c>
     </row>
     <row r="16" spans="3:29" x14ac:dyDescent="0.45">
-      <c r="I16" s="26" t="s">
+      <c r="I16" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="11" t="s">
         <v>57</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="U16" s="47">
+      <c r="U16" s="39">
         <v>29</v>
       </c>
-      <c r="V16" s="40" t="s">
-        <v>114</v>
-      </c>
-      <c r="W16" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="X16" s="50">
+      <c r="V16" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="W16" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="X16" s="42">
         <v>12</v>
       </c>
-      <c r="Y16" s="33" t="s">
+      <c r="Y16" s="29" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="17" spans="9:25" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="I17" s="28" t="s">
+      <c r="I17" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="U17" s="47">
+      <c r="U17" s="39">
         <v>28</v>
       </c>
-      <c r="V17" s="39" t="s">
+      <c r="V17" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="W17" s="44" t="s">
+      <c r="W17" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="X17" s="50">
+      <c r="X17" s="42">
         <v>13</v>
       </c>
-      <c r="Y17" s="33"/>
+      <c r="Y17" s="29"/>
     </row>
     <row r="18" spans="9:25" x14ac:dyDescent="0.45">
       <c r="T18" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="U18" s="47">
+      <c r="U18" s="39">
         <v>27</v>
       </c>
-      <c r="V18" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="W18" s="43" t="s">
-        <v>125</v>
-      </c>
-      <c r="X18" s="50">
+      <c r="V18" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="W18" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="X18" s="42">
         <v>14</v>
       </c>
-      <c r="Y18" s="34" t="s">
+      <c r="Y18" s="29" t="s">
         <v>68</v>
       </c>
     </row>
@@ -7414,19 +7406,19 @@
       <c r="T19" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="U19" s="47">
+      <c r="U19" s="39">
         <v>26</v>
       </c>
-      <c r="V19" s="40" t="s">
-        <v>116</v>
-      </c>
-      <c r="W19" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="X19" s="50">
+      <c r="V19" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="W19" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="X19" s="42">
         <v>15</v>
       </c>
-      <c r="Y19" s="33" t="s">
+      <c r="Y19" s="29" t="s">
         <v>69</v>
       </c>
     </row>
@@ -7434,19 +7426,19 @@
       <c r="T20" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="U20" s="47">
+      <c r="U20" s="39">
         <v>25</v>
       </c>
-      <c r="V20" s="40" t="s">
-        <v>117</v>
-      </c>
-      <c r="W20" s="43" t="s">
-        <v>124</v>
-      </c>
-      <c r="X20" s="50">
+      <c r="V20" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="W20" s="35" t="s">
+        <v>119</v>
+      </c>
+      <c r="X20" s="42">
         <v>16</v>
       </c>
-      <c r="Y20" s="33" t="s">
+      <c r="Y20" s="29" t="s">
         <v>70</v>
       </c>
     </row>
@@ -7454,129 +7446,129 @@
       <c r="T21" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="U21" s="47">
+      <c r="U21" s="39">
         <v>24</v>
       </c>
-      <c r="V21" s="40" t="s">
+      <c r="V21" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="W21" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="W21" s="43" t="s">
-        <v>123</v>
-      </c>
-      <c r="X21" s="50">
+      <c r="X21" s="42">
         <v>17</v>
       </c>
-      <c r="Y21" s="34" t="s">
+      <c r="Y21" s="29" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="22" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="U22" s="47">
+      <c r="U22" s="39">
         <v>23</v>
       </c>
-      <c r="V22" s="39" t="s">
+      <c r="V22" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="W22" s="44" t="s">
+      <c r="W22" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="X22" s="50">
+      <c r="X22" s="42">
         <v>18</v>
       </c>
-      <c r="Y22" s="33"/>
+      <c r="Y22" s="29"/>
     </row>
     <row r="23" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="T23" s="32" t="s">
+      <c r="T23" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="U23" s="47">
+      <c r="U23" s="39">
         <v>22</v>
       </c>
-      <c r="V23" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="W23" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="X23" s="50">
+      <c r="V23" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="W23" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="X23" s="42">
         <v>19</v>
       </c>
-      <c r="Y23" s="10" t="s">
+      <c r="Y23" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="24" spans="9:25" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="T24" s="32" t="s">
+      <c r="T24" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="U24" s="48">
+      <c r="U24" s="40">
         <v>21</v>
       </c>
-      <c r="V24" s="41" t="s">
-        <v>120</v>
-      </c>
-      <c r="W24" s="45" t="s">
-        <v>121</v>
-      </c>
-      <c r="X24" s="51">
+      <c r="V24" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="W24" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="X24" s="43">
         <v>20</v>
       </c>
-      <c r="Y24" s="60" t="s">
+      <c r="Y24" s="52" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="28" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="V28" s="56" t="s">
-        <v>154</v>
-      </c>
-      <c r="W28" s="56"/>
-      <c r="X28" s="59" t="s">
-        <v>155</v>
+      <c r="V28" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="W28" s="48"/>
+      <c r="X28" s="51" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="V30" s="57" t="s">
+      <c r="V30" s="49" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="9:25" x14ac:dyDescent="0.45">
+      <c r="V31" s="48" t="s">
+        <v>140</v>
+      </c>
+      <c r="W31" s="48"/>
+      <c r="X31" s="51" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="9:25" x14ac:dyDescent="0.45">
+      <c r="V32" s="49" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="V33" s="50" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="V34" s="49" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="V35" s="48" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="31" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="V31" s="56" t="s">
-        <v>145</v>
-      </c>
-      <c r="W31" s="56"/>
-      <c r="X31" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="V32" s="57" t="s">
+      <c r="W35" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="X35" s="51" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="33" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="V33" s="58" t="s">
+    <row r="37" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="V37" s="52" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="34" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="V34" s="57" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="35" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="V35" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="W35" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="X35" s="59" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="37" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="V37" s="60" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="38" spans="22:24" x14ac:dyDescent="0.45">
@@ -7584,20 +7576,48 @@
         <v>76</v>
       </c>
       <c r="W38" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="22:24" x14ac:dyDescent="0.45">
       <c r="V39" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="W39" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="22:24" x14ac:dyDescent="0.45">
       <c r="V43" t="s">
+        <v>151</v>
+      </c>
+      <c r="X43" s="28" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="44" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="X44" s="28" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="X45" s="28" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="46" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="X46" s="28" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="47" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="X47" s="28" t="s">
         <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="V48" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -7611,9 +7631,14 @@
     <hyperlink ref="X31" r:id="rId2" display="https://pl.aliexpress.com/item/1005006859633283.html?spm=a2g0o.productlist.main.7.3b25541ei1NHlm&amp;algo_pvid=675fdc6e-635a-43d6-aa33-132ff7e993a6&amp;algo_exp_id=675fdc6e-635a-43d6-aa33-132ff7e993a6-6&amp;pdp_ext_f=%7B%22order%22%3A%22217%22%2C%22spu_best_type%22%3A%22order%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21PLN%2113.91%2112.80%21%21%213.75%213.45%21%40211b61ae17681634404743736e7037%2112000038538341524%21sea%21PL%211839301974%21X%211%210%21n_tag%3A-29919%3Bd%3A36af6a49%3Bm03_new_user%3A-29895%3BpisId%3A5000000198888946&amp;curPageLogUid=Em7yX6pL9y5K&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006859633283%7C_p_origin_prod%3A" xr:uid="{50BDA439-BE9C-4794-94B2-8215B02FE363}"/>
     <hyperlink ref="X35" r:id="rId3" display="https://pl.aliexpress.com/item/1005009999065427.html?spm=a2g0o.productlist.main.1.94c774dbD42auR&amp;algo_pvid=e2a85142-4315-4aa4-9848-02bbcf5f28e9&amp;algo_exp_id=e2a85142-4315-4aa4-9848-02bbcf5f28e9-0&amp;pdp_ext_f=%7B%22order%22%3A%2211%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21PLN%216.29%216.29%21%21%211.70%211.70%21%40211b80e117681635359458265e71ad%2112000050801512683%21sea%21PL%211839301974%21X%211%210%21n_tag%3A-29919%3Bd%3A36af6a49%3Bm03_new_user%3A-29895&amp;curPageLogUid=zQAWtiwlVvfj&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005009999065427%7C_p_origin_prod%3A" xr:uid="{FCD5C859-4829-4FB0-ADC0-DBF330964AB6}"/>
     <hyperlink ref="X28" r:id="rId4" display="https://allegro.pl/produkt/sterownik-waveshare-esp32-s3-pico-0415ba11-c58a-4e15-a465-8a660298ffb0?srsltid=AfmBOoq31e0plBD9E8kJZRmA9ahb_3oByoYm7113zLL9L96nPQW7shj9&amp;dd_referrer=https%3A%2F%2Fwww.google.com%2F&amp;offerId=13793533637" xr:uid="{CC62F130-E55D-4529-A5E1-36DE63956499}"/>
+    <hyperlink ref="X44" r:id="rId5" display="https://botland.com.pl/potencjometry-obrotowe-suwakowe-i-liniowe/307-potencjometr-montazowy-lezacy-10k-5szt-5904422372804.html" xr:uid="{EFCE64E3-C979-4880-947B-652957B1DB8B}"/>
+    <hyperlink ref="X45" r:id="rId6" display="https://botland.com.pl/przelaczniki-przyciskowe-i-elektryczne/14950-przelacznik-monostabilny-pb07c-7x7mm-5-szt-5904422304058.html" xr:uid="{E61796D5-9668-419C-98B4-8863054DB6E6}"/>
+    <hyperlink ref="X46" r:id="rId7" display="https://botland.com.pl/przelaczniki-przyciskowe-i-elektryczne/1416-mikroprzelacznik-bistabilny-on-on-7x7mm-5szt-5904422300005.html" xr:uid="{17EE35BB-B5E5-469A-B6F2-71F29FD9FAE2}"/>
+    <hyperlink ref="X47" r:id="rId8" display="https://botland.com.pl/tact-switch/4784-tact-switch-12x12-7mm-tht-6pin-biale-podswietlenie-5szt-5904422352288.html" xr:uid="{280189A3-27B9-4A58-875D-9F7625958201}"/>
+    <hyperlink ref="X43" r:id="rId9" display="https://botland.com.pl/przelaczniki-spdt/256-przelacznik-suwakowy-esp2010-katowy-5904422372781.html" xr:uid="{7C5073C9-08F5-4338-90C5-B0827C89903C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId5"/>
-  <drawing r:id="rId6"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId10"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>
--- a/wykres_skalowania_joy.xlsx
+++ b/wykres_skalowania_joy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Luke\FlexRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED28FA02-53F7-4454-B6F0-CF2CA3E7E24B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762E7FB1-D219-467C-AA87-CCA1F5CB038D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1763" yWindow="-98" windowWidth="22335" windowHeight="13695" activeTab="3" xr2:uid="{81982E8A-BA81-4862-A7E8-94F1A526E7CC}"/>
   </bookViews>

--- a/wykres_skalowania_joy.xlsx
+++ b/wykres_skalowania_joy.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Luke\FlexRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762E7FB1-D219-467C-AA87-CCA1F5CB038D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72F3CA5-16F5-4FFB-9A2A-5B543AEDF211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1763" yWindow="-98" windowWidth="22335" windowHeight="13695" activeTab="3" xr2:uid="{81982E8A-BA81-4862-A7E8-94F1A526E7CC}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
     <sheet name="Arkusz2" sheetId="2" r:id="rId2"/>
-    <sheet name="Arkusz3" sheetId="3" r:id="rId3"/>
-    <sheet name="Arkusz4" sheetId="4" r:id="rId4"/>
+    <sheet name="keys_ain" sheetId="3" r:id="rId3"/>
+    <sheet name="MCU" sheetId="4" r:id="rId4"/>
+    <sheet name="batt" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="181">
   <si>
     <t>Kolumna1</t>
   </si>
@@ -516,9 +517,6 @@
     <t>ADC1_CH3</t>
   </si>
   <si>
-    <t>ADC1_CH2</t>
-  </si>
-  <si>
     <t>ADC1_CH1</t>
   </si>
   <si>
@@ -576,51 +574,15 @@
     <t>GP12</t>
   </si>
   <si>
-    <t>KEY U</t>
-  </si>
-  <si>
-    <t>KEY L</t>
-  </si>
-  <si>
-    <t>KEY C</t>
-  </si>
-  <si>
-    <t>KEY R</t>
-  </si>
-  <si>
-    <t>KEY D</t>
-  </si>
-  <si>
     <t>5V IN</t>
   </si>
   <si>
-    <t>AP2112K-3.3</t>
-  </si>
-  <si>
-    <t>USB C PD</t>
-  </si>
-  <si>
-    <t>TP5100 (2S CHARGER)</t>
-  </si>
-  <si>
     <t>BMS</t>
   </si>
   <si>
     <t>2x18650</t>
   </si>
   <si>
-    <t>BUCK 5V</t>
-  </si>
-  <si>
-    <t>LDO 3V3</t>
-  </si>
-  <si>
-    <t>1 ~ 10 sztuk TP5100 podwójna pojedyncza bateria litowa kompatybilna z zarządzaniem ładowaniem 2A akumulatorowa płytka litowa - AliExpress</t>
-  </si>
-  <si>
-    <t>10 szt./partia AP2112K-3.3 SOT23-5 AP2112K-3.3TRG1 3.3V 0.6A SOT25 2112 AP2112 AP2113K AP2112-3.3 Dostępne - AliExpress</t>
-  </si>
-  <si>
     <t>buzzer</t>
   </si>
   <si>
@@ -648,9 +610,6 @@
     <t>Mikroprzełącznik bistabilny ON-ON 7x7mm 5szt.</t>
   </si>
   <si>
-    <t>Tact Switch 12x12, 7mm THT 6pin - białe podświetlenie - 5szt.</t>
-  </si>
-  <si>
     <t>Przełącznik suwakowy ESP2010 - kątowy</t>
   </si>
   <si>
@@ -664,6 +623,105 @@
   </si>
   <si>
     <t>3-5x LED RGB</t>
+  </si>
+  <si>
+    <t>CHARGER</t>
+  </si>
+  <si>
+    <t>Wielokomorowy konwerter doładowania USB 2S 3S typu C moduł zasilania płyta ochronna ładowarki LiPo-polimerowej litowo-jonowej - AliExpress 502</t>
+  </si>
+  <si>
+    <t>2S Li-ion 18650 Lithium Battery Charger Protection Board 7.4V Overcurrent Overcharge Overdischarge Protection 4A 2 Series BMS - AliExpress 502</t>
+  </si>
+  <si>
+    <t>AP63203 - przetwornica step-down BabyBuck - 3,3V 2A - SparkFun COM-18357</t>
+  </si>
+  <si>
+    <t>BUCK 3.3V</t>
+  </si>
+  <si>
+    <t>SW_F1</t>
+  </si>
+  <si>
+    <t>SW_F2</t>
+  </si>
+  <si>
+    <t>SW_L1</t>
+  </si>
+  <si>
+    <t>SW_R1</t>
+  </si>
+  <si>
+    <t>SW_C1</t>
+  </si>
+  <si>
+    <t>SW_D1</t>
+  </si>
+  <si>
+    <t>ADC1_CH0</t>
+  </si>
+  <si>
+    <t>POT HALL</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>mid</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>IMU i2c</t>
+  </si>
+  <si>
+    <t>VmaxBatt</t>
+  </si>
+  <si>
+    <t>VminBatt</t>
+  </si>
+  <si>
+    <t>Uain</t>
+  </si>
+  <si>
+    <t>Vbatt</t>
+  </si>
+  <si>
+    <t>AIN</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>VbattMax/(R1+R2)</t>
+  </si>
+  <si>
+    <t>UainMax</t>
+  </si>
+  <si>
+    <t>UainMin</t>
+  </si>
+  <si>
+    <t>nF</t>
+  </si>
+  <si>
+    <t>Ohm</t>
+  </si>
+  <si>
+    <t>mA</t>
+  </si>
+  <si>
+    <t>V*(R2/(R1+R2))</t>
+  </si>
+  <si>
+    <t>AinMax</t>
+  </si>
+  <si>
+    <t>zakres</t>
+  </si>
+  <si>
+    <t>SW_U1</t>
   </si>
 </sst>
 </file>
@@ -791,7 +849,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -812,18 +870,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -972,19 +1024,6 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -1039,12 +1078,92 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1133,16 +1252,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1155,9 +1271,19 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1173,15 +1299,19 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperłącze" xfId="1" builtinId="8"/>
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -4436,7 +4566,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{DAF1ECFE-CD9F-42CD-930D-A24EACC42D82}" name="Kolumna1"/>
     <tableColumn id="2" xr3:uid="{66CF2793-7050-4C9B-B884-EEEDB315E6EA}" name="Kolumna2"/>
-    <tableColumn id="3" xr3:uid="{F468A1AF-5099-44BD-AEE6-18FF806FAB89}" name="Kolumna3" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{F468A1AF-5099-44BD-AEE6-18FF806FAB89}" name="Kolumna3" dataDxfId="3">
       <calculatedColumnFormula>ROUND(Tabela1[[#This Row],[Kolumna1]]*Tabela1[[#This Row],[Kolumna2]]/100,0)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4449,10 +4579,10 @@
   <autoFilter ref="X4:Z58" xr:uid="{AE05E0C3-F770-42CB-B2B0-288F31F7394A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C971093E-EC7C-4443-BC5F-7C781E778E17}" name="Kolumna1"/>
-    <tableColumn id="2" xr3:uid="{7DBF5D29-2FF6-49E3-AF1F-150247CB2E0D}" name="Kolumna2" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{7DBF5D29-2FF6-49E3-AF1F-150247CB2E0D}" name="Kolumna2" dataDxfId="2">
       <calculatedColumnFormula>ROUND((Tabela2[[#This Row],[Kolumna1]])*(Tabela2[[#This Row],[Kolumna1]]/512)^$AA$2*((32767)/512),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{99FA5C64-1251-404D-A592-95560A8DDB3D}" name="Kolumna3" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{99FA5C64-1251-404D-A592-95560A8DDB3D}" name="Kolumna3" dataDxfId="1">
       <calculatedColumnFormula>IF(Tabela2[[#This Row],[Kolumna1]]&lt;=$AB$2,0,ROUND($AC$2 *(((Tabela2[[#This Row],[Kolumna1]]-$AB$2)/($AD$2-$AB$2))^(1+$AA$2)),0))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6882,7 +7012,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2702BDD6-77D0-46D1-94A1-7EBAD4BA6947}">
-  <dimension ref="C1:AC48"/>
+  <dimension ref="C1:AC51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="14.73046875" customWidth="1"/>
@@ -6908,10 +7038,10 @@
       <c r="F2" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="I2" s="53" t="s">
+      <c r="I2" s="60" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="54"/>
+      <c r="J2" s="61"/>
     </row>
     <row r="3" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C3" s="13" t="s">
@@ -6960,12 +7090,12 @@
       <c r="K4" t="s">
         <v>69</v>
       </c>
-      <c r="U4" s="55" t="s">
+      <c r="U4" s="62" t="s">
         <v>99</v>
       </c>
-      <c r="V4" s="56"/>
-      <c r="W4" s="56"/>
-      <c r="X4" s="57"/>
+      <c r="V4" s="63"/>
+      <c r="W4" s="63"/>
+      <c r="X4" s="64"/>
     </row>
     <row r="5" spans="3:29" x14ac:dyDescent="0.45">
       <c r="C5" s="13" t="s">
@@ -6989,26 +7119,26 @@
       <c r="U5" s="38">
         <v>40</v>
       </c>
-      <c r="V5" s="46" t="s">
+      <c r="V5" s="45" t="s">
         <v>100</v>
       </c>
       <c r="W5" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="X5" s="41">
+        <v>129</v>
+      </c>
+      <c r="X5" s="40">
         <v>1</v>
       </c>
       <c r="Y5" s="29" t="s">
-        <v>132</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="3:29" x14ac:dyDescent="0.45">
       <c r="C6" s="13" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D6" s="14"/>
-      <c r="E6" s="58" t="s">
-        <v>160</v>
+      <c r="E6" s="51" t="s">
+        <v>146</v>
       </c>
       <c r="F6" s="15"/>
       <c r="H6" s="9" t="s">
@@ -7023,28 +7153,28 @@
       <c r="K6" t="s">
         <v>71</v>
       </c>
-      <c r="T6" s="44" t="s">
-        <v>137</v>
-      </c>
-      <c r="U6" s="39">
+      <c r="T6" s="43" t="s">
+        <v>131</v>
+      </c>
+      <c r="U6" s="38">
         <v>39</v>
       </c>
       <c r="V6" s="30" t="s">
         <v>101</v>
       </c>
       <c r="W6" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="X6" s="42">
+        <v>130</v>
+      </c>
+      <c r="X6" s="41">
         <v>2</v>
       </c>
       <c r="Y6" s="29" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="3:29" x14ac:dyDescent="0.45">
       <c r="C7" s="13" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="D7" s="14"/>
       <c r="E7" s="14">
@@ -7063,10 +7193,10 @@
       <c r="K7" t="s">
         <v>72</v>
       </c>
-      <c r="T7" s="45" t="s">
+      <c r="T7" s="44" t="s">
         <v>44</v>
       </c>
-      <c r="U7" s="39">
+      <c r="U7" s="38">
         <v>38</v>
       </c>
       <c r="V7" s="31" t="s">
@@ -7075,7 +7205,7 @@
       <c r="W7" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="X7" s="42">
+      <c r="X7" s="41">
         <v>3</v>
       </c>
       <c r="Y7" s="29"/>
@@ -7102,20 +7232,20 @@
         <v>73</v>
       </c>
       <c r="T8" s="9"/>
-      <c r="U8" s="39">
+      <c r="U8" s="38">
         <v>37</v>
       </c>
-      <c r="V8" s="47" t="s">
+      <c r="V8" s="46" t="s">
         <v>102</v>
       </c>
       <c r="W8" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="X8" s="42">
+        <v>125</v>
+      </c>
+      <c r="X8" s="41">
         <v>4</v>
       </c>
       <c r="Y8" s="29" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="3:29" x14ac:dyDescent="0.45">
@@ -7140,20 +7270,20 @@
         <v>74</v>
       </c>
       <c r="T9" s="9"/>
-      <c r="U9" s="39">
+      <c r="U9" s="38">
         <v>36</v>
       </c>
-      <c r="V9" s="47" t="s">
+      <c r="V9" s="46" t="s">
         <v>103</v>
       </c>
       <c r="W9" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="X9" s="42">
+        <v>126</v>
+      </c>
+      <c r="X9" s="41">
         <v>5</v>
       </c>
       <c r="Y9" s="29" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10" spans="3:29" x14ac:dyDescent="0.45">
@@ -7177,20 +7307,20 @@
       <c r="K10" t="s">
         <v>75</v>
       </c>
-      <c r="U10" s="39">
+      <c r="U10" s="38">
         <v>35</v>
       </c>
       <c r="V10" s="32" t="s">
         <v>104</v>
       </c>
       <c r="W10" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="X10" s="42">
+        <v>127</v>
+      </c>
+      <c r="X10" s="41">
         <v>6</v>
       </c>
       <c r="Y10" s="29" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
@@ -7214,21 +7344,19 @@
       <c r="K11" t="s">
         <v>76</v>
       </c>
-      <c r="U11" s="39">
+      <c r="U11" s="38">
         <v>34</v>
       </c>
       <c r="V11" s="32" t="s">
         <v>105</v>
       </c>
       <c r="W11" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="X11" s="42">
+        <v>128</v>
+      </c>
+      <c r="X11" s="41">
         <v>7</v>
       </c>
-      <c r="Y11" s="29" t="s">
-        <v>76</v>
-      </c>
+      <c r="Y11" s="29"/>
     </row>
     <row r="12" spans="3:29" x14ac:dyDescent="0.45">
       <c r="H12" s="9" t="s">
@@ -7243,7 +7371,7 @@
       <c r="K12" t="s">
         <v>77</v>
       </c>
-      <c r="U12" s="39">
+      <c r="U12" s="38">
         <v>33</v>
       </c>
       <c r="V12" s="31" t="s">
@@ -7252,7 +7380,7 @@
       <c r="W12" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="X12" s="42">
+      <c r="X12" s="41">
         <v>8</v>
       </c>
       <c r="Y12" s="29"/>
@@ -7273,16 +7401,16 @@
       <c r="T13" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="U13" s="39">
+      <c r="U13" s="38">
         <v>32</v>
       </c>
       <c r="V13" s="32" t="s">
         <v>106</v>
       </c>
       <c r="W13" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="X13" s="42">
+        <v>121</v>
+      </c>
+      <c r="X13" s="41">
         <v>9</v>
       </c>
       <c r="Y13" s="29" t="s">
@@ -7299,16 +7427,16 @@
       <c r="T14" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="U14" s="39">
+      <c r="U14" s="38">
         <v>31</v>
       </c>
       <c r="V14" s="32" t="s">
         <v>107</v>
       </c>
       <c r="W14" s="35" t="s">
-        <v>123</v>
-      </c>
-      <c r="X14" s="42">
+        <v>122</v>
+      </c>
+      <c r="X14" s="41">
         <v>10</v>
       </c>
       <c r="Y14" s="29" t="s">
@@ -7322,16 +7450,16 @@
       <c r="J15" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="U15" s="39">
+      <c r="U15" s="38">
         <v>30</v>
       </c>
-      <c r="V15" s="47" t="s">
+      <c r="V15" s="46" t="s">
         <v>108</v>
       </c>
       <c r="W15" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="X15" s="42">
+        <v>123</v>
+      </c>
+      <c r="X15" s="41">
         <v>11</v>
       </c>
     </row>
@@ -7345,16 +7473,16 @@
       <c r="T16" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="U16" s="39">
+      <c r="U16" s="38">
         <v>29</v>
       </c>
       <c r="V16" s="32" t="s">
         <v>109</v>
       </c>
       <c r="W16" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="X16" s="42">
+        <v>124</v>
+      </c>
+      <c r="X16" s="41">
         <v>12</v>
       </c>
       <c r="Y16" s="29" t="s">
@@ -7368,7 +7496,7 @@
       <c r="J17" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="U17" s="39">
+      <c r="U17" s="38">
         <v>28</v>
       </c>
       <c r="V17" s="31" t="s">
@@ -7377,25 +7505,28 @@
       <c r="W17" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="X17" s="42">
+      <c r="X17" s="41">
         <v>13</v>
       </c>
       <c r="Y17" s="29"/>
     </row>
     <row r="18" spans="9:25" x14ac:dyDescent="0.45">
+      <c r="R18" t="s">
+        <v>160</v>
+      </c>
       <c r="T18" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="U18" s="39">
+      <c r="U18" s="38">
         <v>27</v>
       </c>
       <c r="V18" s="32" t="s">
         <v>110</v>
       </c>
       <c r="W18" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="X18" s="42">
+        <v>119</v>
+      </c>
+      <c r="X18" s="41">
         <v>14</v>
       </c>
       <c r="Y18" s="29" t="s">
@@ -7403,19 +7534,25 @@
       </c>
     </row>
     <row r="19" spans="9:25" x14ac:dyDescent="0.45">
+      <c r="R19" t="s">
+        <v>161</v>
+      </c>
+      <c r="S19">
+        <v>0.47</v>
+      </c>
       <c r="T19" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="U19" s="39">
+      <c r="U19" s="38">
         <v>26</v>
       </c>
       <c r="V19" s="32" t="s">
         <v>111</v>
       </c>
       <c r="W19" s="35" t="s">
-        <v>121</v>
-      </c>
-      <c r="X19" s="42">
+        <v>120</v>
+      </c>
+      <c r="X19" s="41">
         <v>15</v>
       </c>
       <c r="Y19" s="29" t="s">
@@ -7423,19 +7560,25 @@
       </c>
     </row>
     <row r="20" spans="9:25" x14ac:dyDescent="0.45">
+      <c r="R20" t="s">
+        <v>162</v>
+      </c>
+      <c r="S20">
+        <v>1.3049999999999999</v>
+      </c>
       <c r="T20" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="U20" s="39">
+      <c r="U20" s="38">
         <v>25</v>
       </c>
       <c r="V20" s="32" t="s">
         <v>112</v>
       </c>
       <c r="W20" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="X20" s="42">
+        <v>118</v>
+      </c>
+      <c r="X20" s="41">
         <v>16</v>
       </c>
       <c r="Y20" s="29" t="s">
@@ -7443,19 +7586,25 @@
       </c>
     </row>
     <row r="21" spans="9:25" x14ac:dyDescent="0.45">
+      <c r="R21" t="s">
+        <v>163</v>
+      </c>
+      <c r="S21">
+        <v>2.2000000000000002</v>
+      </c>
       <c r="T21" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="U21" s="39">
+      <c r="U21" s="38">
         <v>24</v>
       </c>
       <c r="V21" s="32" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="W21" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="X21" s="42">
+        <v>117</v>
+      </c>
+      <c r="X21" s="41">
         <v>17</v>
       </c>
       <c r="Y21" s="29" t="s">
@@ -7463,7 +7612,7 @@
       </c>
     </row>
     <row r="22" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="U22" s="39">
+      <c r="U22" s="38">
         <v>23</v>
       </c>
       <c r="V22" s="31" t="s">
@@ -7472,25 +7621,28 @@
       <c r="W22" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="X22" s="42">
+      <c r="X22" s="41">
         <v>18</v>
       </c>
       <c r="Y22" s="29"/>
     </row>
     <row r="23" spans="9:25" x14ac:dyDescent="0.45">
+      <c r="R23" t="s">
+        <v>164</v>
+      </c>
       <c r="T23" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="U23" s="39">
+        <v>153</v>
+      </c>
+      <c r="U23" s="38">
         <v>22</v>
       </c>
       <c r="V23" s="32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="W23" s="35" t="s">
-        <v>117</v>
-      </c>
-      <c r="X23" s="42">
+        <v>116</v>
+      </c>
+      <c r="X23" s="41">
         <v>19</v>
       </c>
       <c r="Y23" t="s">
@@ -7499,76 +7651,47 @@
     </row>
     <row r="24" spans="9:25" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="T24" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="U24" s="40">
+        <v>154</v>
+      </c>
+      <c r="U24" s="39">
         <v>21</v>
       </c>
       <c r="V24" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="W24" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="W24" s="37" t="s">
-        <v>116</v>
-      </c>
-      <c r="X24" s="43">
+      <c r="X24" s="42">
         <v>20</v>
       </c>
-      <c r="Y24" s="52" t="s">
-        <v>75</v>
-      </c>
+      <c r="Y24" s="50"/>
     </row>
     <row r="28" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="V28" s="48" t="s">
-        <v>149</v>
-      </c>
-      <c r="W28" s="48"/>
-      <c r="X28" s="51" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="V30" s="49" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="31" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="V31" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="W31" s="48"/>
-      <c r="X31" s="51" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="9:25" x14ac:dyDescent="0.45">
-      <c r="V32" s="49" t="s">
-        <v>141</v>
+      <c r="V28" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="W28" s="47"/>
+      <c r="X28" s="49" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="33" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="V33" s="50" t="s">
-        <v>142</v>
+      <c r="V33" s="48" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="34" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="V34" s="49" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="V35" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="W35" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="X35" s="51" t="s">
-        <v>146</v>
+      <c r="V34" s="47" t="s">
+        <v>152</v>
+      </c>
+      <c r="X34" s="28" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="37" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="V37" s="52" t="s">
-        <v>147</v>
+      <c r="V37" s="50" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="22:24" x14ac:dyDescent="0.45">
@@ -7576,51 +7699,68 @@
         <v>76</v>
       </c>
       <c r="W38" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="22:24" x14ac:dyDescent="0.45">
       <c r="V39" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="W39" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="22:24" x14ac:dyDescent="0.45">
       <c r="V43" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="X43" s="28" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" spans="22:24" x14ac:dyDescent="0.45">
       <c r="X44" s="28" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="45" spans="22:24" x14ac:dyDescent="0.45">
       <c r="X45" s="28" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="46" spans="22:24" x14ac:dyDescent="0.45">
       <c r="X46" s="28" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="47" spans="22:24" x14ac:dyDescent="0.45">
-      <c r="X47" s="28" t="s">
-        <v>156</v>
-      </c>
+      <c r="X47" s="28"/>
     </row>
     <row r="48" spans="22:24" x14ac:dyDescent="0.45">
       <c r="V48" t="s">
-        <v>158</v>
+        <v>144</v>
+      </c>
+    </row>
+    <row r="50" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="V50" t="s">
+        <v>132</v>
+      </c>
+      <c r="X50" s="28" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="51" spans="22:24" x14ac:dyDescent="0.45">
+      <c r="V51" t="s">
+        <v>148</v>
+      </c>
+      <c r="X51" s="28" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AN8:AN46">
+    <sortCondition ref="AN7:AN46"/>
+  </sortState>
   <mergeCells count="2">
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="U4:X4"/>
@@ -7628,17 +7768,228 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="AC3" r:id="rId1" location="Overview" display="https://www.waveshare.com/wiki/ESP32-S3-Pico - Overview" xr:uid="{33A4DEBB-0A14-4DAE-AA88-61F330874481}"/>
-    <hyperlink ref="X31" r:id="rId2" display="https://pl.aliexpress.com/item/1005006859633283.html?spm=a2g0o.productlist.main.7.3b25541ei1NHlm&amp;algo_pvid=675fdc6e-635a-43d6-aa33-132ff7e993a6&amp;algo_exp_id=675fdc6e-635a-43d6-aa33-132ff7e993a6-6&amp;pdp_ext_f=%7B%22order%22%3A%22217%22%2C%22spu_best_type%22%3A%22order%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21PLN%2113.91%2112.80%21%21%213.75%213.45%21%40211b61ae17681634404743736e7037%2112000038538341524%21sea%21PL%211839301974%21X%211%210%21n_tag%3A-29919%3Bd%3A36af6a49%3Bm03_new_user%3A-29895%3BpisId%3A5000000198888946&amp;curPageLogUid=Em7yX6pL9y5K&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005006859633283%7C_p_origin_prod%3A" xr:uid="{50BDA439-BE9C-4794-94B2-8215B02FE363}"/>
-    <hyperlink ref="X35" r:id="rId3" display="https://pl.aliexpress.com/item/1005009999065427.html?spm=a2g0o.productlist.main.1.94c774dbD42auR&amp;algo_pvid=e2a85142-4315-4aa4-9848-02bbcf5f28e9&amp;algo_exp_id=e2a85142-4315-4aa4-9848-02bbcf5f28e9-0&amp;pdp_ext_f=%7B%22order%22%3A%2211%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21PLN%216.29%216.29%21%21%211.70%211.70%21%40211b80e117681635359458265e71ad%2112000050801512683%21sea%21PL%211839301974%21X%211%210%21n_tag%3A-29919%3Bd%3A36af6a49%3Bm03_new_user%3A-29895&amp;curPageLogUid=zQAWtiwlVvfj&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005009999065427%7C_p_origin_prod%3A" xr:uid="{FCD5C859-4829-4FB0-ADC0-DBF330964AB6}"/>
-    <hyperlink ref="X28" r:id="rId4" display="https://allegro.pl/produkt/sterownik-waveshare-esp32-s3-pico-0415ba11-c58a-4e15-a465-8a660298ffb0?srsltid=AfmBOoq31e0plBD9E8kJZRmA9ahb_3oByoYm7113zLL9L96nPQW7shj9&amp;dd_referrer=https%3A%2F%2Fwww.google.com%2F&amp;offerId=13793533637" xr:uid="{CC62F130-E55D-4529-A5E1-36DE63956499}"/>
-    <hyperlink ref="X44" r:id="rId5" display="https://botland.com.pl/potencjometry-obrotowe-suwakowe-i-liniowe/307-potencjometr-montazowy-lezacy-10k-5szt-5904422372804.html" xr:uid="{EFCE64E3-C979-4880-947B-652957B1DB8B}"/>
-    <hyperlink ref="X45" r:id="rId6" display="https://botland.com.pl/przelaczniki-przyciskowe-i-elektryczne/14950-przelacznik-monostabilny-pb07c-7x7mm-5-szt-5904422304058.html" xr:uid="{E61796D5-9668-419C-98B4-8863054DB6E6}"/>
-    <hyperlink ref="X46" r:id="rId7" display="https://botland.com.pl/przelaczniki-przyciskowe-i-elektryczne/1416-mikroprzelacznik-bistabilny-on-on-7x7mm-5szt-5904422300005.html" xr:uid="{17EE35BB-B5E5-469A-B6F2-71F29FD9FAE2}"/>
-    <hyperlink ref="X47" r:id="rId8" display="https://botland.com.pl/tact-switch/4784-tact-switch-12x12-7mm-tht-6pin-biale-podswietlenie-5szt-5904422352288.html" xr:uid="{280189A3-27B9-4A58-875D-9F7625958201}"/>
-    <hyperlink ref="X43" r:id="rId9" display="https://botland.com.pl/przelaczniki-spdt/256-przelacznik-suwakowy-esp2010-katowy-5904422372781.html" xr:uid="{7C5073C9-08F5-4338-90C5-B0827C89903C}"/>
+    <hyperlink ref="X28" r:id="rId2" display="https://allegro.pl/produkt/sterownik-waveshare-esp32-s3-pico-0415ba11-c58a-4e15-a465-8a660298ffb0?srsltid=AfmBOoq31e0plBD9E8kJZRmA9ahb_3oByoYm7113zLL9L96nPQW7shj9&amp;dd_referrer=https%3A%2F%2Fwww.google.com%2F&amp;offerId=13793533637" xr:uid="{CC62F130-E55D-4529-A5E1-36DE63956499}"/>
+    <hyperlink ref="X44" r:id="rId3" display="https://botland.com.pl/potencjometry-obrotowe-suwakowe-i-liniowe/307-potencjometr-montazowy-lezacy-10k-5szt-5904422372804.html" xr:uid="{EFCE64E3-C979-4880-947B-652957B1DB8B}"/>
+    <hyperlink ref="X45" r:id="rId4" display="https://botland.com.pl/przelaczniki-przyciskowe-i-elektryczne/14950-przelacznik-monostabilny-pb07c-7x7mm-5-szt-5904422304058.html" xr:uid="{E61796D5-9668-419C-98B4-8863054DB6E6}"/>
+    <hyperlink ref="X46" r:id="rId5" display="https://botland.com.pl/przelaczniki-przyciskowe-i-elektryczne/1416-mikroprzelacznik-bistabilny-on-on-7x7mm-5szt-5904422300005.html" xr:uid="{17EE35BB-B5E5-469A-B6F2-71F29FD9FAE2}"/>
+    <hyperlink ref="X43" r:id="rId6" display="https://botland.com.pl/przelaczniki-spdt/256-przelacznik-suwakowy-esp2010-katowy-5904422372781.html" xr:uid="{7C5073C9-08F5-4338-90C5-B0827C89903C}"/>
+    <hyperlink ref="X51" r:id="rId7" display="https://pl.aliexpress.com/item/1005005976542467.html?pdp_ext_f=%7B%22sku_id%22%3A%2212000035135022810%22%7D&amp;sourceType=1&amp;spm=a2g0o.wish-manage-home.0.0&amp;gatewayAdapt=glo2pol" xr:uid="{CA1D0FAC-3A41-46C3-A1F5-57A229C92918}"/>
+    <hyperlink ref="X50" r:id="rId8" display="https://pl.aliexpress.com/item/33017997012.html?pdp_ext_f=%7B%22sku_id%22%3A%2212000034759723851%22%7D&amp;sourceType=1&amp;spm=a2g0o.wish-manage-home.0.0&amp;gatewayAdapt=glo2pol" xr:uid="{7E6C689E-071E-4FDC-88D9-1D562DD62594}"/>
+    <hyperlink ref="X34" r:id="rId9" display="https://botland.com.pl/przetwornice-step-down/20235-ap63203-przetwornica-step-down-babybuck-33v-2a-sparkfun-com-18357-5904422352097.html" xr:uid="{ED749321-3B62-4338-B817-6F180ADAB35A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
   <drawing r:id="rId11"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA4CCA43-065D-4405-A3CC-730632208A7D}">
+  <dimension ref="C2:N19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="2" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C2" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2">
+        <v>3.3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D3">
+        <v>8.4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" s="53" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7" t="s">
+        <v>171</v>
+      </c>
+      <c r="G7" s="52"/>
+      <c r="H7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="G8" s="52"/>
+      <c r="H8" s="55"/>
+      <c r="I8" s="56" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9">
+        <v>33000</v>
+      </c>
+      <c r="E9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G9" s="52"/>
+      <c r="H9" t="s">
+        <v>25</v>
+      </c>
+      <c r="I9" s="57"/>
+      <c r="J9" s="58"/>
+    </row>
+    <row r="10" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>10000</v>
+      </c>
+      <c r="E10" t="s">
+        <v>175</v>
+      </c>
+      <c r="G10" s="52"/>
+      <c r="H10" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="59" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>9100</v>
+      </c>
+      <c r="G11" s="54" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="59"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12">
+        <v>1000</v>
+      </c>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13">
+        <v>1000</v>
+      </c>
+      <c r="E13" t="s">
+        <v>175</v>
+      </c>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14">
+        <v>100</v>
+      </c>
+      <c r="E14" t="s">
+        <v>174</v>
+      </c>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="16" spans="3:14" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="6">
+        <f>D3*((D10+D11+D12)/(D9+(D10+D11+D12)))</f>
+        <v>3.1796610169491526</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="6">
+        <f>D4*((D10+D11+D12)/(D9+(D10+D11+D12)))</f>
+        <v>2.2711864406779663</v>
+      </c>
+      <c r="E17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C18" t="s">
+        <v>179</v>
+      </c>
+      <c r="D18" s="6">
+        <f>D16-D17</f>
+        <v>0.90847457627118633</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
+        <v>170</v>
+      </c>
+      <c r="D19" s="6">
+        <f>D3/(D9+(D10+D11+D12))*1000</f>
+        <v>0.15819209039548021</v>
+      </c>
+      <c r="E19" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D16:D17">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>$D$2-0.1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/wykres_skalowania_joy.xlsx
+++ b/wykres_skalowania_joy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Luke\FlexRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C72F3CA5-16F5-4FFB-9A2A-5B543AEDF211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E81130-956D-427F-A552-0E875B86B3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1763" yWindow="-98" windowWidth="22335" windowHeight="13695" activeTab="3" xr2:uid="{81982E8A-BA81-4862-A7E8-94F1A526E7CC}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="keys_ain" sheetId="3" r:id="rId3"/>
     <sheet name="MCU" sheetId="4" r:id="rId4"/>
     <sheet name="batt" sheetId="5" r:id="rId5"/>
+    <sheet name="photoR" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="191">
   <si>
     <t>Kolumna1</t>
   </si>
@@ -722,6 +723,36 @@
   </si>
   <si>
     <t>SW_U1</t>
+  </si>
+  <si>
+    <t>light R</t>
+  </si>
+  <si>
+    <t>dark R</t>
+  </si>
+  <si>
+    <t>voltage</t>
+  </si>
+  <si>
+    <t>resistor</t>
+  </si>
+  <si>
+    <t>light V</t>
+  </si>
+  <si>
+    <t>dark V</t>
+  </si>
+  <si>
+    <t>photoR</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>output</t>
+  </si>
+  <si>
+    <t>TOP VIEW</t>
   </si>
 </sst>
 </file>
@@ -875,7 +906,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1158,12 +1189,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1297,6 +1365,54 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7012,7 +7128,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2702BDD6-77D0-46D1-94A1-7EBAD4BA6947}">
-  <dimension ref="C1:AC51"/>
+  <dimension ref="C1:AC84"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="14.73046875" customWidth="1"/>
@@ -7741,7 +7857,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="50" spans="22:24" x14ac:dyDescent="0.45">
+    <row r="50" spans="21:24" x14ac:dyDescent="0.45">
       <c r="V50" t="s">
         <v>132</v>
       </c>
@@ -7749,21 +7865,320 @@
         <v>150</v>
       </c>
     </row>
-    <row r="51" spans="22:24" x14ac:dyDescent="0.45">
+    <row r="51" spans="21:24" x14ac:dyDescent="0.45">
       <c r="V51" t="s">
         <v>148</v>
       </c>
       <c r="X51" s="28" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="62" spans="21:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="63" spans="21:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="U63" s="82" t="s">
+        <v>190</v>
+      </c>
+      <c r="V63" s="83"/>
+      <c r="W63" s="83"/>
+      <c r="X63" s="84"/>
+    </row>
+    <row r="64" spans="21:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="U64" s="65" t="s">
+        <v>99</v>
+      </c>
+      <c r="V64" s="66"/>
+      <c r="W64" s="66"/>
+      <c r="X64" s="67"/>
+    </row>
+    <row r="65" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U65" s="68">
+        <v>21</v>
+      </c>
+      <c r="V65" s="72" t="s">
+        <v>114</v>
+      </c>
+      <c r="W65" s="78" t="s">
+        <v>115</v>
+      </c>
+      <c r="X65" s="69">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="66" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U66" s="13">
+        <v>22</v>
+      </c>
+      <c r="V66" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="W66" s="79" t="s">
+        <v>116</v>
+      </c>
+      <c r="X66" s="70">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U67" s="13">
+        <v>23</v>
+      </c>
+      <c r="V67" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="W67" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="X67" s="70">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="68" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U68" s="13">
+        <v>24</v>
+      </c>
+      <c r="V68" s="73" t="s">
+        <v>159</v>
+      </c>
+      <c r="W68" s="79" t="s">
+        <v>117</v>
+      </c>
+      <c r="X68" s="70">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U69" s="13">
+        <v>25</v>
+      </c>
+      <c r="V69" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="W69" s="79" t="s">
+        <v>118</v>
+      </c>
+      <c r="X69" s="70">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U70" s="13">
+        <v>26</v>
+      </c>
+      <c r="V70" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="W70" s="79" t="s">
+        <v>120</v>
+      </c>
+      <c r="X70" s="70">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="71" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U71" s="13">
+        <v>27</v>
+      </c>
+      <c r="V71" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="W71" s="79" t="s">
+        <v>119</v>
+      </c>
+      <c r="X71" s="70">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="72" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U72" s="13">
+        <v>28</v>
+      </c>
+      <c r="V72" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="W72" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="X72" s="70">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U73" s="13">
+        <v>29</v>
+      </c>
+      <c r="V73" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="W73" s="79" t="s">
+        <v>124</v>
+      </c>
+      <c r="X73" s="70">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U74" s="13">
+        <v>30</v>
+      </c>
+      <c r="V74" s="75" t="s">
+        <v>108</v>
+      </c>
+      <c r="W74" s="79" t="s">
+        <v>123</v>
+      </c>
+      <c r="X74" s="70">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U75" s="13">
+        <v>31</v>
+      </c>
+      <c r="V75" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="W75" s="79" t="s">
+        <v>122</v>
+      </c>
+      <c r="X75" s="70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U76" s="13">
+        <v>32</v>
+      </c>
+      <c r="V76" s="73" t="s">
+        <v>106</v>
+      </c>
+      <c r="W76" s="79" t="s">
+        <v>121</v>
+      </c>
+      <c r="X76" s="70">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U77" s="13">
+        <v>33</v>
+      </c>
+      <c r="V77" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="W77" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="X77" s="70">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U78" s="13">
+        <v>34</v>
+      </c>
+      <c r="V78" s="73" t="s">
+        <v>105</v>
+      </c>
+      <c r="W78" s="79" t="s">
+        <v>128</v>
+      </c>
+      <c r="X78" s="70">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U79" s="13">
+        <v>35</v>
+      </c>
+      <c r="V79" s="73" t="s">
+        <v>104</v>
+      </c>
+      <c r="W79" s="79" t="s">
+        <v>127</v>
+      </c>
+      <c r="X79" s="70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U80" s="13">
+        <v>36</v>
+      </c>
+      <c r="V80" s="75" t="s">
+        <v>103</v>
+      </c>
+      <c r="W80" s="79" t="s">
+        <v>126</v>
+      </c>
+      <c r="X80" s="70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U81" s="13">
+        <v>37</v>
+      </c>
+      <c r="V81" s="75" t="s">
+        <v>102</v>
+      </c>
+      <c r="W81" s="79" t="s">
+        <v>125</v>
+      </c>
+      <c r="X81" s="70">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U82" s="13">
+        <v>38</v>
+      </c>
+      <c r="V82" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="W82" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="X82" s="70">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="21:24" x14ac:dyDescent="0.45">
+      <c r="U83" s="13">
+        <v>39</v>
+      </c>
+      <c r="V83" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="W83" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="X83" s="70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" spans="21:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="U84" s="16">
+        <v>40</v>
+      </c>
+      <c r="V84" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="W84" s="81" t="s">
+        <v>129</v>
+      </c>
+      <c r="X84" s="71">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="AN8:AN46">
     <sortCondition ref="AN7:AN46"/>
   </sortState>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="U4:X4"/>
+    <mergeCell ref="U64:X64"/>
+    <mergeCell ref="U63:X63"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
@@ -7777,7 +8192,8 @@
     <hyperlink ref="X50" r:id="rId8" display="https://pl.aliexpress.com/item/33017997012.html?pdp_ext_f=%7B%22sku_id%22%3A%2212000034759723851%22%7D&amp;sourceType=1&amp;spm=a2g0o.wish-manage-home.0.0&amp;gatewayAdapt=glo2pol" xr:uid="{7E6C689E-071E-4FDC-88D9-1D562DD62594}"/>
     <hyperlink ref="X34" r:id="rId9" display="https://botland.com.pl/przetwornice-step-down/20235-ap63203-przetwornica-step-down-babybuck-33v-2a-sparkfun-com-18357-5904422352097.html" xr:uid="{ED749321-3B62-4338-B817-6F180ADAB35A}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId10"/>
   <drawing r:id="rId11"/>
 </worksheet>
@@ -7992,4 +8408,123 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66F1A510-6B58-4DEF-A3A3-211BA2917046}">
+  <dimension ref="B2:J16"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="3" width="10.796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="1">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C5">
+        <v>800000</v>
+      </c>
+      <c r="G5" s="56" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G6" s="52"/>
+      <c r="H6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7">
+        <v>10000</v>
+      </c>
+      <c r="G7" s="52"/>
+      <c r="J7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="G8" s="52"/>
+      <c r="H8" s="58" t="s">
+        <v>184</v>
+      </c>
+      <c r="I8" s="57"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C9">
+        <f>(C2*C4)/(C4+C7)</f>
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G9" s="57" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="1">
+        <f>(C2*C5)/(C5+C7)</f>
+        <v>3.2592592592592591</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14">
+        <f>D14*1000</f>
+        <v>800000</v>
+      </c>
+      <c r="D14">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15">
+        <f>D15*1000</f>
+        <v>10000</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C16" s="1">
+        <f>(C2*C14)/(C14+C15)</f>
+        <v>3.2592592592592591</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/wykres_skalowania_joy.xlsx
+++ b/wykres_skalowania_joy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Luke\FlexRC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E81130-956D-427F-A552-0E875B86B3B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{998B16F6-84B4-42B3-82AE-20B404570CEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1763" yWindow="-98" windowWidth="22335" windowHeight="13695" activeTab="3" xr2:uid="{81982E8A-BA81-4862-A7E8-94F1A526E7CC}"/>
   </bookViews>
@@ -1352,30 +1352,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1405,6 +1381,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -7154,10 +7154,10 @@
       <c r="F2" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="I2" s="60" t="s">
+      <c r="I2" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="61"/>
+      <c r="J2" s="75"/>
     </row>
     <row r="3" spans="3:29" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C3" s="13" t="s">
@@ -7206,12 +7206,12 @@
       <c r="K4" t="s">
         <v>69</v>
       </c>
-      <c r="U4" s="62" t="s">
+      <c r="U4" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="V4" s="63"/>
-      <c r="W4" s="63"/>
-      <c r="X4" s="64"/>
+      <c r="V4" s="77"/>
+      <c r="W4" s="77"/>
+      <c r="X4" s="78"/>
     </row>
     <row r="5" spans="3:29" x14ac:dyDescent="0.45">
       <c r="C5" s="13" t="s">
@@ -7883,24 +7883,24 @@
       <c r="X63" s="84"/>
     </row>
     <row r="64" spans="21:24" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="U64" s="65" t="s">
+      <c r="U64" s="79" t="s">
         <v>99</v>
       </c>
-      <c r="V64" s="66"/>
-      <c r="W64" s="66"/>
-      <c r="X64" s="67"/>
+      <c r="V64" s="80"/>
+      <c r="W64" s="80"/>
+      <c r="X64" s="81"/>
     </row>
     <row r="65" spans="21:24" x14ac:dyDescent="0.45">
-      <c r="U65" s="68">
+      <c r="U65" s="60">
         <v>21</v>
       </c>
-      <c r="V65" s="72" t="s">
+      <c r="V65" s="64" t="s">
         <v>114</v>
       </c>
-      <c r="W65" s="78" t="s">
+      <c r="W65" s="70" t="s">
         <v>115</v>
       </c>
-      <c r="X65" s="69">
+      <c r="X65" s="61">
         <v>20</v>
       </c>
     </row>
@@ -7908,13 +7908,13 @@
       <c r="U66" s="13">
         <v>22</v>
       </c>
-      <c r="V66" s="73" t="s">
+      <c r="V66" s="65" t="s">
         <v>113</v>
       </c>
-      <c r="W66" s="79" t="s">
+      <c r="W66" s="71" t="s">
         <v>116</v>
       </c>
-      <c r="X66" s="70">
+      <c r="X66" s="62">
         <v>19</v>
       </c>
     </row>
@@ -7922,13 +7922,13 @@
       <c r="U67" s="13">
         <v>23</v>
       </c>
-      <c r="V67" s="74" t="s">
+      <c r="V67" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="W67" s="80" t="s">
+      <c r="W67" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="X67" s="70">
+      <c r="X67" s="62">
         <v>18</v>
       </c>
     </row>
@@ -7936,13 +7936,13 @@
       <c r="U68" s="13">
         <v>24</v>
       </c>
-      <c r="V68" s="73" t="s">
+      <c r="V68" s="65" t="s">
         <v>159</v>
       </c>
-      <c r="W68" s="79" t="s">
+      <c r="W68" s="71" t="s">
         <v>117</v>
       </c>
-      <c r="X68" s="70">
+      <c r="X68" s="62">
         <v>17</v>
       </c>
     </row>
@@ -7950,13 +7950,13 @@
       <c r="U69" s="13">
         <v>25</v>
       </c>
-      <c r="V69" s="73" t="s">
+      <c r="V69" s="65" t="s">
         <v>112</v>
       </c>
-      <c r="W69" s="79" t="s">
+      <c r="W69" s="71" t="s">
         <v>118</v>
       </c>
-      <c r="X69" s="70">
+      <c r="X69" s="62">
         <v>16</v>
       </c>
     </row>
@@ -7964,13 +7964,13 @@
       <c r="U70" s="13">
         <v>26</v>
       </c>
-      <c r="V70" s="73" t="s">
+      <c r="V70" s="65" t="s">
         <v>111</v>
       </c>
-      <c r="W70" s="79" t="s">
+      <c r="W70" s="71" t="s">
         <v>120</v>
       </c>
-      <c r="X70" s="70">
+      <c r="X70" s="62">
         <v>15</v>
       </c>
     </row>
@@ -7978,13 +7978,13 @@
       <c r="U71" s="13">
         <v>27</v>
       </c>
-      <c r="V71" s="73" t="s">
+      <c r="V71" s="65" t="s">
         <v>110</v>
       </c>
-      <c r="W71" s="79" t="s">
+      <c r="W71" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="X71" s="70">
+      <c r="X71" s="62">
         <v>14</v>
       </c>
     </row>
@@ -7992,13 +7992,13 @@
       <c r="U72" s="13">
         <v>28</v>
       </c>
-      <c r="V72" s="74" t="s">
+      <c r="V72" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="W72" s="80" t="s">
+      <c r="W72" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="X72" s="70">
+      <c r="X72" s="62">
         <v>13</v>
       </c>
     </row>
@@ -8006,13 +8006,13 @@
       <c r="U73" s="13">
         <v>29</v>
       </c>
-      <c r="V73" s="73" t="s">
+      <c r="V73" s="65" t="s">
         <v>109</v>
       </c>
-      <c r="W73" s="79" t="s">
+      <c r="W73" s="71" t="s">
         <v>124</v>
       </c>
-      <c r="X73" s="70">
+      <c r="X73" s="62">
         <v>12</v>
       </c>
     </row>
@@ -8020,13 +8020,13 @@
       <c r="U74" s="13">
         <v>30</v>
       </c>
-      <c r="V74" s="75" t="s">
+      <c r="V74" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="W74" s="79" t="s">
+      <c r="W74" s="71" t="s">
         <v>123</v>
       </c>
-      <c r="X74" s="70">
+      <c r="X74" s="62">
         <v>11</v>
       </c>
     </row>
@@ -8034,13 +8034,13 @@
       <c r="U75" s="13">
         <v>31</v>
       </c>
-      <c r="V75" s="73" t="s">
+      <c r="V75" s="65" t="s">
         <v>107</v>
       </c>
-      <c r="W75" s="79" t="s">
+      <c r="W75" s="71" t="s">
         <v>122</v>
       </c>
-      <c r="X75" s="70">
+      <c r="X75" s="62">
         <v>10</v>
       </c>
     </row>
@@ -8048,13 +8048,13 @@
       <c r="U76" s="13">
         <v>32</v>
       </c>
-      <c r="V76" s="73" t="s">
+      <c r="V76" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="W76" s="79" t="s">
+      <c r="W76" s="71" t="s">
         <v>121</v>
       </c>
-      <c r="X76" s="70">
+      <c r="X76" s="62">
         <v>9</v>
       </c>
     </row>
@@ -8062,13 +8062,13 @@
       <c r="U77" s="13">
         <v>33</v>
       </c>
-      <c r="V77" s="74" t="s">
+      <c r="V77" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="W77" s="80" t="s">
+      <c r="W77" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="X77" s="70">
+      <c r="X77" s="62">
         <v>8</v>
       </c>
     </row>
@@ -8076,13 +8076,13 @@
       <c r="U78" s="13">
         <v>34</v>
       </c>
-      <c r="V78" s="73" t="s">
+      <c r="V78" s="65" t="s">
         <v>105</v>
       </c>
-      <c r="W78" s="79" t="s">
+      <c r="W78" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="X78" s="70">
+      <c r="X78" s="62">
         <v>7</v>
       </c>
     </row>
@@ -8090,13 +8090,13 @@
       <c r="U79" s="13">
         <v>35</v>
       </c>
-      <c r="V79" s="73" t="s">
+      <c r="V79" s="65" t="s">
         <v>104</v>
       </c>
-      <c r="W79" s="79" t="s">
+      <c r="W79" s="71" t="s">
         <v>127</v>
       </c>
-      <c r="X79" s="70">
+      <c r="X79" s="62">
         <v>6</v>
       </c>
     </row>
@@ -8104,13 +8104,13 @@
       <c r="U80" s="13">
         <v>36</v>
       </c>
-      <c r="V80" s="75" t="s">
+      <c r="V80" s="67" t="s">
         <v>103</v>
       </c>
-      <c r="W80" s="79" t="s">
+      <c r="W80" s="71" t="s">
         <v>126</v>
       </c>
-      <c r="X80" s="70">
+      <c r="X80" s="62">
         <v>5</v>
       </c>
     </row>
@@ -8118,13 +8118,13 @@
       <c r="U81" s="13">
         <v>37</v>
       </c>
-      <c r="V81" s="75" t="s">
+      <c r="V81" s="67" t="s">
         <v>102</v>
       </c>
-      <c r="W81" s="79" t="s">
+      <c r="W81" s="71" t="s">
         <v>125</v>
       </c>
-      <c r="X81" s="70">
+      <c r="X81" s="62">
         <v>4</v>
       </c>
     </row>
@@ -8132,13 +8132,13 @@
       <c r="U82" s="13">
         <v>38</v>
       </c>
-      <c r="V82" s="74" t="s">
+      <c r="V82" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="W82" s="80" t="s">
+      <c r="W82" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="X82" s="70">
+      <c r="X82" s="62">
         <v>3</v>
       </c>
     </row>
@@ -8146,13 +8146,13 @@
       <c r="U83" s="13">
         <v>39</v>
       </c>
-      <c r="V83" s="76" t="s">
+      <c r="V83" s="68" t="s">
         <v>101</v>
       </c>
-      <c r="W83" s="79" t="s">
+      <c r="W83" s="71" t="s">
         <v>130</v>
       </c>
-      <c r="X83" s="70">
+      <c r="X83" s="62">
         <v>2</v>
       </c>
     </row>
@@ -8160,13 +8160,13 @@
       <c r="U84" s="16">
         <v>40</v>
       </c>
-      <c r="V84" s="77" t="s">
+      <c r="V84" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="W84" s="81" t="s">
+      <c r="W84" s="73" t="s">
         <v>129</v>
       </c>
-      <c r="X84" s="71">
+      <c r="X84" s="63">
         <v>1</v>
       </c>
     </row>
